--- a/Report_Sample/Annual planning.xlsx
+++ b/Report_Sample/Annual planning.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hackathon2026\report_generate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hackathon2026\report_generate\Report_Sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E123BFA7-7C29-49F0-B77F-01069E0DB290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCB4428-C2BB-4081-BE3A-3CB0A1BA493A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B7103582-030B-48C7-9E46-06BDDB2E6FC8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>No</t>
   </si>
@@ -144,31 +144,13 @@
   <si>
     <t>(1) %Submission/Traffic +2pp
 (2) Average Ticket size +10%</t>
-  </si>
-  <si>
-    <t>PIC</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Status change</t>
-  </si>
-  <si>
-    <t>New timing (if applicable)</t>
-  </si>
-  <si>
-    <t>Details from that month</t>
-  </si>
-  <si>
-    <t>How confident</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,71 +189,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFDDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor rgb="FFDDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFDDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFCE4D6"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -311,7 +235,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -342,21 +266,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
@@ -674,21 +583,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DF190EA-9C98-4CE4-ABC9-78C20E14A160}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="39.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.77734375" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.109375" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="16" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -701,40 +605,16 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -747,14 +627,8 @@
       <c r="D3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -767,14 +641,8 @@
       <c r="D4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -787,14 +655,8 @@
       <c r="D5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>4</v>
       </c>
@@ -807,28 +669,16 @@
       <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>5</v>
       </c>
@@ -841,14 +691,8 @@
       <c r="D8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>6</v>
       </c>
@@ -861,14 +705,8 @@
       <c r="D9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>7</v>
       </c>
@@ -881,14 +719,8 @@
       <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>8</v>
       </c>
@@ -901,14 +733,8 @@
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>9</v>
       </c>
@@ -921,14 +747,8 @@
       <c r="D12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>10</v>
       </c>
@@ -941,14 +761,8 @@
       <c r="D13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>11</v>
       </c>
@@ -961,14 +775,8 @@
       <c r="D14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>12</v>
       </c>
@@ -981,14 +789,8 @@
       <c r="D15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
